--- a/data/trans_bre/P1805_2016_2023-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1805_2016_2023-Provincia-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,61</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125,31%</t>
+          <t>163,39%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 7,76</t>
+          <t>0,14; 7,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,33</t>
+          <t>-0,22; 3,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 380,91</t>
+          <t>-2,29; 375,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,17; 903,32</t>
+          <t>-26,29; 896,91</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,91</t>
+          <t>-0,26; 1,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 2,71</t>
+          <t>-2,53; 2,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-78,83; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,25; 109,5</t>
+          <t>-49,44; 132,58</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 6,1</t>
+          <t>0,31; 6,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,21</t>
+          <t>-0,99; 4,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 911,54</t>
+          <t>-7,14; 1026,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 325,66</t>
+          <t>-21,5; 256,93</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-1,99</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-30,38%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,15</t>
+          <t>-1,49; 3,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 1,55</t>
+          <t>-3,9; 3,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,8; 230,01</t>
+          <t>-46,11; 282,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,36; 38,75</t>
+          <t>-48,06; 94,27</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103,09%</t>
+          <t>105,07%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 1,24</t>
+          <t>-4,62; 1,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,27</t>
+          <t>-0,74; 2,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-90,23; 130,41</t>
+          <t>-89,35; 143,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,17; —</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,64</t>
+          <t>0,29; 5,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,93</t>
+          <t>-1,57; 3,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1469,13</t>
+          <t>-31,47; 1386,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,7; 209,54</t>
+          <t>-43,28; 216,69</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,27</t>
+          <t>0,85; 4,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 3,39</t>
+          <t>-1,12; 4,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,46; 928,89</t>
+          <t>24,53; 837,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-56,12; 90,76</t>
+          <t>-23,27; 136,0</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,22</t>
+          <t>0,47; 4,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,52</t>
+          <t>-1,39; 1,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,39; 262,36</t>
+          <t>6,75; 273,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 289,79</t>
+          <t>-42,13; 89,85</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,8</t>
+          <t>1,17; 2,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,86</t>
+          <t>-0,15; 1,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49,87; 189,32</t>
+          <t>54,0; 184,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 74,69</t>
+          <t>-4,4; 65,6</t>
         </is>
       </c>
     </row>
